--- a/docs/downloads/11/tbl_degats_champs_riz_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,12 +367,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Beaucoup</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Rien</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Beaucoup</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -394,14 +394,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>14.3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -418,17 +418,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C3">
-        <v>85.7</v>
+        <v>33.3</v>
       </c>
       <c r="D3">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -442,44 +442,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="D4">
-        <v>33.3</v>
+        <v>7.3</v>
       </c>
       <c r="E4">
-        <v>66.7</v>
+        <v>31.7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C5">
-        <v>7.3</v>
+        <v>22.2</v>
       </c>
       <c r="D5">
-        <v>51.2</v>
+        <v>77.8</v>
       </c>
       <c r="E5">
-        <v>31.7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -490,17 +490,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33.3</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -514,41 +514,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C7">
-        <v>75</v>
+        <v>53.3</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C8">
-        <v>77.8</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>22.2</v>
+        <v>40</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -557,22 +557,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>15.4</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>61.5</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -581,25 +581,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C10">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>53.3</v>
+        <v>85.7</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>14.3</v>
       </c>
       <c r="F10">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -610,17 +610,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>64.7</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>29.4</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -634,17 +634,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C12">
-        <v>15.4</v>
+        <v>28.6</v>
       </c>
       <c r="D12">
-        <v>23.1</v>
+        <v>14.3</v>
       </c>
       <c r="E12">
-        <v>61.5</v>
+        <v>57.1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -658,17 +658,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C13">
-        <v>85.7</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E13">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -682,17 +682,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C14">
-        <v>64.7</v>
+        <v>15.8</v>
       </c>
       <c r="D14">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="E14">
-        <v>29.4</v>
+        <v>73.7</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -706,65 +706,65 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C15">
-        <v>14.3</v>
+        <v>75.3</v>
       </c>
       <c r="D15">
-        <v>28.6</v>
+        <v>1.1</v>
       </c>
       <c r="E15">
-        <v>57.1</v>
+        <v>11.2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C16">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>15.8</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>73.7</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>1.1</v>
+        <v>70.3</v>
       </c>
       <c r="D18">
-        <v>75.3</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="F18">
-        <v>12.4</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -806,37 +806,37 @@
         </is>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D19">
-        <v>83.3</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>23.1</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -845,22 +845,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Criquets</t>
         </is>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>17.6</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -869,22 +869,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -893,25 +893,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="D23">
-        <v>70.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E23">
-        <v>10.9</v>
+        <v>23.1</v>
       </c>
       <c r="F23">
-        <v>18.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -922,20 +922,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D24">
-        <v>84.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F24">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -946,17 +946,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C25">
-        <v>46.2</v>
+        <v>9.5</v>
       </c>
       <c r="D25">
-        <v>30.8</v>
+        <v>90.5</v>
       </c>
       <c r="E25">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -970,17 +970,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Criquets</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C26">
-        <v>11.8</v>
+        <v>22.9</v>
       </c>
       <c r="D26">
-        <v>17.6</v>
+        <v>5.7</v>
       </c>
       <c r="E26">
-        <v>70.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -994,139 +994,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C27">
-        <v>75</v>
+        <v>66.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>17.4</v>
       </c>
       <c r="F27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Facteur humain</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="D28">
-        <v>3.8</v>
-      </c>
-      <c r="E28">
-        <v>23.1</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Inondation</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>20</v>
-      </c>
-      <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29">
-        <v>40</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Maladie</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>90.5</v>
-      </c>
-      <c r="D30">
-        <v>9.5</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>5.7</v>
-      </c>
-      <c r="D31">
-        <v>22.9</v>
-      </c>
-      <c r="E31">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>3.6</v>
-      </c>
-      <c r="D32">
-        <v>66.5</v>
-      </c>
-      <c r="E32">
-        <v>17.4</v>
-      </c>
-      <c r="F32">
         <v>12.5</v>
       </c>
     </row>

--- a/docs/downloads/11/tbl_degats_champs_riz_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_marovoay_tous.xlsx
@@ -389,7 +389,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -413,7 +413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -437,7 +437,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,7 +557,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -797,7 +797,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,7 +869,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
